--- a/doc/primitives.xlsx
+++ b/doc/primitives.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\david\BeagleST\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B8A24D2-F36B-4BA1-BF67-44BA0FA8C3EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6165535-C579-4FDC-BEFE-0098E220D2DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="348" yWindow="1020" windowWidth="29736" windowHeight="18600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="468" yWindow="432" windowWidth="43104" windowHeight="23880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="144">
   <si>
     <t>#define</t>
   </si>
@@ -465,6 +465,9 @@
   </si>
   <si>
     <t>PRIM_FLOAT_EXP</t>
+  </si>
+  <si>
+    <t>PRIM_MICROSECONDS</t>
   </si>
 </sst>
 </file>
@@ -782,7 +785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C142"/>
+  <dimension ref="A1:C143"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="45" bestFit="1" customWidth="1"/>
@@ -1799,10 +1802,10 @@
         <v>0</v>
       </c>
       <c r="B93" t="s">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="C93">
-        <v>420</v>
+        <v>412</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
@@ -1810,10 +1813,10 @@
         <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C94">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
@@ -1821,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="B95" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C95">
-        <v>501</v>
+        <v>421</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
@@ -1832,10 +1835,10 @@
         <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C96">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
@@ -1843,10 +1846,10 @@
         <v>0</v>
       </c>
       <c r="B97" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C97">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
@@ -1854,10 +1857,10 @@
         <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C98">
-        <v>548</v>
+        <v>503</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
@@ -1865,10 +1868,10 @@
         <v>0</v>
       </c>
       <c r="B99" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C99">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
@@ -1876,10 +1879,10 @@
         <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C100">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
@@ -1887,10 +1890,10 @@
         <v>0</v>
       </c>
       <c r="B101" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C101">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
@@ -1898,10 +1901,10 @@
         <v>0</v>
       </c>
       <c r="B102" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C102">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
@@ -1909,10 +1912,10 @@
         <v>0</v>
       </c>
       <c r="B103" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C103">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
@@ -1920,10 +1923,10 @@
         <v>0</v>
       </c>
       <c r="B104" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C104">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
@@ -1931,10 +1934,10 @@
         <v>0</v>
       </c>
       <c r="B105" t="s">
-        <v>119</v>
+        <v>29</v>
       </c>
       <c r="C105">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
@@ -1942,10 +1945,10 @@
         <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C106">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
@@ -1953,10 +1956,10 @@
         <v>0</v>
       </c>
       <c r="B107" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C107">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
@@ -1964,10 +1967,10 @@
         <v>0</v>
       </c>
       <c r="B108" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C108">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
@@ -1975,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="B109" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C109">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
@@ -1986,10 +1989,10 @@
         <v>0</v>
       </c>
       <c r="B110" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="C110">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
@@ -1997,10 +2000,10 @@
         <v>0</v>
       </c>
       <c r="B111" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C111">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
@@ -2008,10 +2011,10 @@
         <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C112">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
@@ -2019,10 +2022,10 @@
         <v>0</v>
       </c>
       <c r="B113" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C113">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
@@ -2030,10 +2033,10 @@
         <v>0</v>
       </c>
       <c r="B114" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C114">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
@@ -2041,10 +2044,10 @@
         <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C115">
-        <v>569</v>
+        <v>564</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
@@ -2052,10 +2055,10 @@
         <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C116">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
@@ -2063,10 +2066,10 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>124</v>
+        <v>58</v>
       </c>
       <c r="C117">
-        <v>600</v>
+        <v>570</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
@@ -2074,10 +2077,10 @@
         <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C118">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
@@ -2085,10 +2088,10 @@
         <v>0</v>
       </c>
       <c r="B119" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C119">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
@@ -2096,10 +2099,10 @@
         <v>0</v>
       </c>
       <c r="B120" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C120">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
@@ -2107,10 +2110,10 @@
         <v>0</v>
       </c>
       <c r="B121" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C121">
-        <v>610</v>
+        <v>603</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
@@ -2118,10 +2121,10 @@
         <v>0</v>
       </c>
       <c r="B122" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C122">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
@@ -2129,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="B123" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C123">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
@@ -2140,10 +2143,10 @@
         <v>0</v>
       </c>
       <c r="B124" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="C124">
-        <v>700</v>
+        <v>612</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
@@ -2151,10 +2154,10 @@
         <v>0</v>
       </c>
       <c r="B125" t="s">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="C125">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
@@ -2162,10 +2165,10 @@
         <v>0</v>
       </c>
       <c r="B126" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C126">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
@@ -2173,10 +2176,10 @@
         <v>0</v>
       </c>
       <c r="B127" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="C127">
-        <v>1403</v>
+        <v>702</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
@@ -2184,10 +2187,10 @@
         <v>0</v>
       </c>
       <c r="B128" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="C128">
-        <v>1500</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
@@ -2195,10 +2198,10 @@
         <v>0</v>
       </c>
       <c r="B129" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C129">
-        <v>1501</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
@@ -2206,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="B130" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C130">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
@@ -2217,10 +2220,10 @@
         <v>0</v>
       </c>
       <c r="B131" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C131">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
@@ -2228,10 +2231,10 @@
         <v>0</v>
       </c>
       <c r="B132" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C132">
-        <v>1504</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
@@ -2239,10 +2242,10 @@
         <v>0</v>
       </c>
       <c r="B133" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C133">
-        <v>1505</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
@@ -2250,10 +2253,10 @@
         <v>0</v>
       </c>
       <c r="B134" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C134">
-        <v>1506</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
@@ -2261,10 +2264,10 @@
         <v>0</v>
       </c>
       <c r="B135" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C135">
-        <v>1507</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
@@ -2272,10 +2275,10 @@
         <v>0</v>
       </c>
       <c r="B136" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C136">
-        <v>1508</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
@@ -2283,10 +2286,10 @@
         <v>0</v>
       </c>
       <c r="B137" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C137">
-        <v>1509</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
@@ -2294,10 +2297,10 @@
         <v>0</v>
       </c>
       <c r="B138" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="C138">
-        <v>1510</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
@@ -2305,10 +2308,10 @@
         <v>0</v>
       </c>
       <c r="B139" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C139">
-        <v>1511</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
@@ -2316,10 +2319,10 @@
         <v>0</v>
       </c>
       <c r="B140" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C140">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
@@ -2327,10 +2330,10 @@
         <v>0</v>
       </c>
       <c r="B141" t="s">
-        <v>61</v>
+        <v>115</v>
       </c>
       <c r="C141">
-        <v>2000</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
@@ -2338,15 +2341,26 @@
         <v>0</v>
       </c>
       <c r="B142" t="s">
+        <v>61</v>
+      </c>
+      <c r="C142">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>0</v>
+      </c>
+      <c r="B143" t="s">
         <v>118</v>
       </c>
-      <c r="C142">
+      <c r="C143">
         <v>4096</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C142">
-    <sortCondition ref="C2:C142"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C143">
+    <sortCondition ref="C2:C143"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
